--- a/static/templates/planilha_colaboradores_modelo.xlsx
+++ b/static/templates/planilha_colaboradores_modelo.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Menu Importar → Excluir por planilha. Apenas coluna Registration/Matrícula.</t>
+          <t>Importar → Excluir por planilha. Use excluir_colaboradores_lista.xlsx (NÃO Fechamento de Ponto).</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,14 +723,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>ESP-999</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>ESP-777</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESP-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>

--- a/static/templates/planilha_colaboradores_modelo.xlsx
+++ b/static/templates/planilha_colaboradores_modelo.xlsx
@@ -427,43 +427,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nome Completo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Matrícula</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Telefone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Código do Vendedor</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CostCenter</t>
+          <t>Cargo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Turno Operacional</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Data Admissão</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Data Nascimento</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aniversário</t>
         </is>
       </c>
     </row>
@@ -480,25 +490,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>(31) 99940-9789</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MOTORISTA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Souza Pinto</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Souza Pinto</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>01/03/2024</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>15/07/1990</t>
         </is>
@@ -517,25 +537,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>31999887766</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>AJUDANTE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Exemplar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Exemplar</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>10/01/2025</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -548,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,136 +596,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Name (obrigatório)</t>
+          <t>Nome Completo (obrigatório)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nome completo do colaborador (será gravado em maiúsculas).</t>
+          <t>Igual ao formulário na tela. Nome será gravado em maiúsculas.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Registration (obrigatório)</t>
+          <t>Matrícula (obrigatório)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matrícula única no sistema. Não repita na mesma planilha.</t>
+          <t>Matrícula única. Não repetir na planilha.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Role (obrigatório)</t>
+          <t>Telefone</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cargo/função (ex.: MOTORISTA, AJUDANTE). Cadastre funções em /funcoes se precisar.</t>
+          <t>DDD + número. Ex.: (31) 99940-9789 ou 31999409789. Opcional.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Código do Vendedor</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manhã, Tarde ou Noite. Padrão: Manhã.</t>
+          <t>Para importação de devoluções. Ex.: 110, 201. Opcional.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CostCenter</t>
+          <t>Cargo (obrigatório)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empresa/centro de custo: Souza Pinto, Exemplar, Geral, Outubro 2020, etc.</t>
+          <t>Ex.: MOTORISTA, AJUDANTE. Cadastre em /funcoes se precisar.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Admissão</t>
+          <t>Empresa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opcional. Formato dd/mm/aaaa.</t>
+          <t>Souza Pinto, Exemplar, Geral, Outubro 2020, etc. Padrão: Souza Pinto.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Nascimento</t>
+          <t>Turno Operacional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opcional. Formato dd/mm/aaaa.</t>
+          <t>Manhã, Tarde ou Noite. Padrão: Manhã.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Admissão</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Formato dd/mm/aaaa. Opcional.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turno (Shift)</t>
+          <t>Aniversário</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Valores aceitos: Manhã | Tarde | Noite</t>
+          <t>Data de nascimento, dd/mm/aaaa. Opcional.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Empresa (CostCenter)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Use o nome exato da empresa como aparece nos cards da tela Colaboradores.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Importação</t>
+          <t>Empresa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Na tela Colaboradores → Importar → Planilha Excel. Só insere matrículas novas.</t>
+          <t>Use o nome exato como nos cards da tela Colaboradores.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Turno Operacional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Valores aceitos: Manhã | Tarde | Noite</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Importação</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Colaboradores → Importar → Planilha Excel. Só matrículas novas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Exclusão em lote</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Importar → Excluir por planilha. Use excluir_colaboradores_lista.xlsx (NÃO Fechamento de Ponto).</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Menu Excluir por planilha — não use Fechamento de Ponto.</t>
         </is>
       </c>
     </row>
@@ -716,7 +770,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Matrícula</t>
         </is>
       </c>
     </row>
